--- a/tech/java/Java.xlsx
+++ b/tech/java/Java.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/doc/tech/java/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/tech/java/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E41620-1F3C-D94B-8D92-673DE80F7E9A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749F6572-6380-9A48-B174-A00E41372549}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="460" windowWidth="27660" windowHeight="17540" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="1140" yWindow="460" windowWidth="27660" windowHeight="17540" activeTab="5" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="6" r:id="rId1"/>

--- a/tech/java/Java.xlsx
+++ b/tech/java/Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/tech/java/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749F6572-6380-9A48-B174-A00E41372549}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C437AA9-7B6C-A042-9B07-AF16EF37ADC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="460" windowWidth="27660" windowHeight="17540" activeTab="5" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="7" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="6" r:id="rId1"/>
@@ -26,6 +26,14 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
